--- a/artfynd/A 6054-2025 artfynd.xlsx
+++ b/artfynd/A 6054-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>64564765</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>789599.7709344591</v>
+        <v>789600</v>
       </c>
       <c r="R2" t="n">
-        <v>7088000.846130515</v>
+        <v>7088001</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,19 +745,9 @@
           <t>2017-03-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-03-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -820,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67208218</v>
+        <v>118680360</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,39 +816,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>3277</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>stigarna S Snöcksmyran, Holmöarna, Vb</t>
+          <t>Klockstapeln, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>789323.698002578</v>
+        <v>788902</v>
       </c>
       <c r="R3" t="n">
-        <v>7087989.098956426</v>
+        <v>7087913</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,22 +873,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-08-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,31 +894,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Hansson</t>
+          <t>Christer Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Hansson</t>
+          <t>Christer Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117487584</v>
+        <v>122846784</v>
       </c>
       <c r="B4" t="n">
-        <v>57558</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -970,7 +936,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -983,17 +949,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmö kyrkogård - skogsbryn, Holmöarna, Vb</t>
+          <t>Holmökyrka, Holmö by, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789049</v>
+        <v>789028</v>
       </c>
       <c r="R4" t="n">
-        <v>7087954</v>
+        <v>7087924</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,19 +986,9 @@
           <t>2024-06-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,19 +1003,15 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Hansson</t>
+          <t>Marcus Östman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Hansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Holmöarnas arter</t>
-        </is>
-      </c>
+          <t>Per Hansson, Jonas Lundberg, Random Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6054-2025 artfynd.xlsx
+++ b/artfynd/A 6054-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64564765</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680360</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,8 +1027,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122846784</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>